--- a/data/trans_camb/P19-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 3,88</t>
+          <t>-5,07; 3,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 11,05</t>
+          <t>1,18; 10,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,5</t>
+          <t>-4,99; 4,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 3,64</t>
+          <t>-6,57; 3,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 8,38</t>
+          <t>-1,41; 8,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,3</t>
+          <t>-6,49; 2,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 2,48</t>
+          <t>-4,31; 2,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,84</t>
+          <t>1,12; 8,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 2,36</t>
+          <t>-4,14; 2,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 19,52</t>
+          <t>-20,38; 17,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 55,06</t>
+          <t>4,51; 49,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 27,08</t>
+          <t>-20,34; 22,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 12,81</t>
+          <t>-20,09; 12,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 29,39</t>
+          <t>-4,38; 30,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 11,44</t>
+          <t>-18,9; 9,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 9,74</t>
+          <t>-15,07; 9,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 30,46</t>
+          <t>3,36; 32,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 9,55</t>
+          <t>-14,67; 10,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 2,56</t>
+          <t>-4,68; 2,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,4</t>
+          <t>-0,57; 7,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,39; 1,03</t>
+          <t>-14,9; 1,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 3,2</t>
+          <t>-5,24; 2,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 8,3</t>
+          <t>-0,02; 8,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 0,31</t>
+          <t>-7,61; 0,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,83</t>
+          <t>-4,2; 1,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,81</t>
+          <t>0,62; 6,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -1,11</t>
+          <t>-13,01; -0,92</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 11,05</t>
+          <t>-18,16; 12,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 32,1</t>
+          <t>-2,16; 32,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 4,11</t>
+          <t>-56,64; 4,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 10,99</t>
+          <t>-15,63; 10,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 28,28</t>
+          <t>0,1; 28,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 1,16</t>
+          <t>-22,71; 1,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 6,79</t>
+          <t>-13,95; 6,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 25,94</t>
+          <t>2,16; 24,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,17; -4,23</t>
+          <t>-45,29; -3,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 3,57</t>
+          <t>-6,23; 3,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 8,99</t>
+          <t>-1,08; 8,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 10,33</t>
+          <t>-1,03; 10,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 1,87</t>
+          <t>-7,89; 1,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 7,09</t>
+          <t>-2,25; 7,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 6,93</t>
+          <t>-18,37; 7,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,5</t>
+          <t>-5,68; 1,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 6,21</t>
+          <t>-0,12; 6,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 6,22</t>
+          <t>-8,99; 6,4</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 14,36</t>
+          <t>-20,84; 14,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 36,8</t>
+          <t>-3,74; 35,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 42,29</t>
+          <t>-3,49; 40,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 6,01</t>
+          <t>-22,96; 5,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 23,7</t>
+          <t>-6,38; 24,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,67; 21,55</t>
+          <t>-54,0; 23,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 5,41</t>
+          <t>-17,64; 4,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 21,87</t>
+          <t>-0,28; 22,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 21,15</t>
+          <t>-29,13; 21,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 5,01</t>
+          <t>-2,49; 6,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,01; 8,27</t>
+          <t>-0,16; 7,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 8,62</t>
+          <t>0,16; 8,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 5,84</t>
+          <t>-3,05; 5,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 6,47</t>
+          <t>-2,06; 6,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 6,48</t>
+          <t>-4,42; 6,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,22</t>
+          <t>-1,58; 4,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 6,01</t>
+          <t>0,26; 5,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 6,49</t>
+          <t>-0,55; 6,34</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 21,57</t>
+          <t>-9,4; 27,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 36,35</t>
+          <t>-0,66; 33,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 37,77</t>
+          <t>0,64; 37,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 20,67</t>
+          <t>-9,07; 19,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 22,62</t>
+          <t>-6,42; 22,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 21,89</t>
+          <t>-13,84; 23,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 15,77</t>
+          <t>-5,42; 15,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 22,58</t>
+          <t>0,92; 22,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 24,59</t>
+          <t>-1,86; 23,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,0</t>
+          <t>-2,31; 2,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,63</t>
+          <t>2,09; 6,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 3,23</t>
+          <t>-5,32; 3,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,4</t>
+          <t>-3,33; 1,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,43</t>
+          <t>0,88; 5,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,87</t>
+          <t>-7,14; 1,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,12</t>
+          <t>-2,06; 0,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,35</t>
+          <t>2,07; 5,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,62</t>
+          <t>-4,41; 1,67</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 8,5</t>
+          <t>-9,0; 8,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,74; 27,76</t>
+          <t>7,97; 26,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 13,16</t>
+          <t>-20,55; 13,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 4,68</t>
+          <t>-10,3; 4,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,79; 18,19</t>
+          <t>2,66; 18,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 6,12</t>
+          <t>-22,18; 5,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 4,08</t>
+          <t>-7,12; 3,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6,48; 19,46</t>
+          <t>7,11; 19,09</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 5,82</t>
+          <t>-15,29; 6,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-2,3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-1,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,62</t>
+          <t>-5,23; 3,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,49</t>
+          <t>1,32; 10,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 4,77</t>
+          <t>-5,87; 3,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 3,62</t>
+          <t>-7,08; 3,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 8,7</t>
+          <t>-1,64; 8,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 2,62</t>
+          <t>-7,45; 2,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,35</t>
+          <t>-4,63; 2,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,12</t>
+          <t>1,14; 7,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 2,65</t>
+          <t>-4,64; 2,21</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,31%</t>
+          <t>-2,36%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-5,4%</t>
+          <t>-7,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-2,81%</t>
+          <t>-4,85%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 17,79</t>
+          <t>-20,79; 16,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 49,48</t>
+          <t>5,0; 50,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 22,99</t>
+          <t>-22,49; 17,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 12,7</t>
+          <t>-20,9; 11,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 30,82</t>
+          <t>-4,85; 28,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 9,39</t>
+          <t>-21,5; 7,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 9,11</t>
+          <t>-16,31; 10,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 32,02</t>
+          <t>4,13; 31,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 10,34</t>
+          <t>-16,04; 9,0</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,78</t>
+          <t>-4,27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,1</t>
+          <t>-2,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,86</t>
+          <t>-5,5; 2,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 7,64</t>
+          <t>-0,81; 7,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 1,14</t>
+          <t>-5,06; 3,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,99</t>
+          <t>-5,57; 2,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 8,44</t>
+          <t>-0,08; 8,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 0,37</t>
+          <t>-8,23; -0,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,73</t>
+          <t>-4,15; 1,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,46</t>
+          <t>1,12; 6,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -0,92</t>
+          <t>-5,58; 0,43</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-22,1%</t>
+          <t>-3,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-12,02%</t>
+          <t>-13,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,1%</t>
+          <t>-9,31%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 12,28</t>
+          <t>-20,66; 10,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 32,79</t>
+          <t>-2,92; 32,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-56,64; 4,42</t>
+          <t>-18,88; 15,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 10,12</t>
+          <t>-16,7; 8,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 28,96</t>
+          <t>-0,24; 29,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 1,32</t>
+          <t>-24,74; -1,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 6,55</t>
+          <t>-13,99; 6,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 24,29</t>
+          <t>3,81; 25,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,29; -3,44</t>
+          <t>-18,42; 1,71</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>2,53</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>1,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 3,7</t>
+          <t>-5,75; 3,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 8,6</t>
+          <t>-1,38; 8,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 10,29</t>
+          <t>-2,8; 7,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1,77</t>
+          <t>-8,26; 1,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 7,39</t>
+          <t>-2,3; 7,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 7,62</t>
+          <t>-3,81; 5,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 1,25</t>
+          <t>-5,41; 1,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 6,47</t>
+          <t>-0,23; 6,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 6,4</t>
+          <t>-1,64; 5,52</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-10,72%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 14,91</t>
+          <t>-19,26; 15,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 35,08</t>
+          <t>-4,56; 35,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 40,88</t>
+          <t>-9,38; 31,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 5,83</t>
+          <t>-24,13; 5,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 24,48</t>
+          <t>-6,82; 25,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-54,0; 23,87</t>
+          <t>-10,72; 19,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 4,77</t>
+          <t>-17,38; 4,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 22,64</t>
+          <t>-0,62; 24,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 21,98</t>
+          <t>-5,19; 19,58</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,22</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>4,06</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>4,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 6,11</t>
+          <t>-2,83; 5,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 7,87</t>
+          <t>0,19; 7,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 8,66</t>
+          <t>0,38; 8,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 5,62</t>
+          <t>-2,74; 5,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 6,42</t>
+          <t>-1,85; 6,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 6,7</t>
+          <t>-0,29; 7,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,07</t>
+          <t>-1,56; 4,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,93</t>
+          <t>0,43; 6,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 6,34</t>
+          <t>1,48; 7,1</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 27,01</t>
+          <t>-10,03; 24,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 33,93</t>
+          <t>0,79; 35,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 37,22</t>
+          <t>1,43; 37,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 19,32</t>
+          <t>-8,37; 18,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 22,74</t>
+          <t>-5,66; 21,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 23,2</t>
+          <t>-0,89; 26,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 15,5</t>
+          <t>-5,4; 16,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 22,65</t>
+          <t>1,42; 24,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 23,92</t>
+          <t>5,02; 27,3</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,0</t>
+          <t>-2,65; 2,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,41</t>
+          <t>1,81; 6,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,2</t>
+          <t>-1,09; 3,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,24</t>
+          <t>-3,16; 1,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,43</t>
+          <t>0,89; 5,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,68</t>
+          <t>-2,35; 1,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,96</t>
+          <t>-2,21; 0,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,26</t>
+          <t>2,01; 5,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,67</t>
+          <t>-0,81; 2,22</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,71%</t>
+          <t>-0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 8,38</t>
+          <t>-10,05; 8,54</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7,97; 26,84</t>
+          <t>7,02; 26,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 13,1</t>
+          <t>-4,2; 14,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 4,17</t>
+          <t>-9,7; 4,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,66; 18,04</t>
+          <t>2,66; 17,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 5,39</t>
+          <t>-7,18; 6,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 3,46</t>
+          <t>-7,69; 3,5</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7,11; 19,09</t>
+          <t>6,82; 19,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 6,12</t>
+          <t>-2,77; 8,14</t>
         </is>
       </c>
     </row>
